--- a/script_NX/constraint/ULTRA300_BGA484_TUT_EGSE_top_signals.xlsx
+++ b/script_NX/constraint/ULTRA300_BGA484_TUT_EGSE_top_signals.xlsx
@@ -11,9 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assignments" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Assignments'!$A$1:$D$64</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1138,14 +1136,12 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>A11
-i_sys_clk</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>A12
-i_config_clk</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -1375,26 +1371,22 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>C10
-o_spectrum_bit</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>C11
-o_spectrum_wr_en</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>C12
-o_spectrum_clk</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>C13
-o_spectrum_sof</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1404,20 +1396,17 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>C15
-o_spectrum_sd_bit</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>C16
-o_spectrum_sd_wr_en</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>C17
-o_spectrum_sd_clk</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1528,8 +1517,7 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>D15
-o_spectrum_sd_sof</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1669,20 +1657,17 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>E19
-i_config_bit</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>E20
-i_config_wr_en</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="V6" s="8" t="inlineStr">
         <is>
-          <t>E21
-i_config_sof</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -2396,12 +2381,14 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L21
+o_spectrum_sd_bit</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L22
+o_spectrum_sd_wr_en</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2502,14 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>M21</t>
+          <t>M21
+o_spectrum_sd_clk</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>M22</t>
+          <t>M22
+o_spectrum_sd_sof</t>
         </is>
       </c>
     </row>
@@ -2744,22 +2733,26 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P19
+i_config_clk</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P20
+i_config_bit</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P21
+i_config_wr_en</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P22
+i_config_sof</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2856,8 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R19
+i_reset</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2984,22 +2978,26 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T19
+o_spectrum_bit</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T20
+o_spectrum_wr_en</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T21
+o_spectrum_clk</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T22
+o_spectrum_sof</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3674,8 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>AB15</t>
+          <t>AB15
+i_sys_clk</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3715,6 +3714,8 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
@@ -3764,1425 +3765,1396 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Package net name</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Top VHDL signal</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IOB14_D17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>o_sck(1)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IOB14_D21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>i_sdi(1)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IOB14_D14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>o_cs_n(2)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IOB14_D23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>o_sck(3)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IOB14_D05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>i_sdi(3)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IOB12_D09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>i_sdi(4)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IOB12_D08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>o_cs_n(5)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IOB12_D07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>o_sck(6)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IOB12_D06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>i_sdi(6)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>IOB14_D22</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>o_sck(0)</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IOB14_D19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>o_cs_n(0)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IOB14_D15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>i_sdi(0)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IOB14_D13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>o_cs_n(1)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IOB14_D11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>o_sck(2)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IOB14_D18</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>i_sdi(2)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IOB14_D03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>o_cs_n(3)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IOB12_D23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>o_sck(4)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IOB12_D19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>o_cs_n(4)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IOB12_D10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>o_sck(5)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IOB12_D11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>i_sdi(5)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IOB12_D12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>o_cs_n(6)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>IOB14_D20</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>o_DAC_SCLK(0)</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>DAC</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IOB14_D16</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(0)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IOB14_D10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(0)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IOB14_D08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(1)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IOB14_D09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(1)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IOB14_D01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(1)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IOB14_D04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(5)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IOB14_D02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(5)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IOB13_D12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>o_DAC_SCLK(4)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IOB13_D11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(4)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IOB13_D03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(4)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IOB13_D09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>o_DAC_SCLK(6)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IOB12_D22</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>o_DAC_SCLK(2)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IOB12_D20</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(2)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IOB12_D18</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(2)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>IOB12_D15</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(3)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IOB12_D13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(3)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>IOB12_D03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(6)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IOB14_D12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(0)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IOB14_D07</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>o_DAC_SCLK(1)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IOB14_D00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>o_DAC_SCLK(5)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IOB13_D13</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(4)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>IOB13_D14</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>o_DAC_on_off(5)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IOB13_D15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(6)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IOB12_D21</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>o_DAC_SYNC_n(2)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IOB12_D17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>o_DAC_SCLK(3)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IOB12_D16</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(3)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>V4</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IOB12_D14</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>o_DAC_DIN(6)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>IOB15_D09P_CLK</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>i_sys_clk</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Clock</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>A12</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>IOB15_D08P_CLK</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IOB08_D13</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>i_config_clk</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>Clock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D19</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(0)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D16</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(0)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D12</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(0)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D15</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(0)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D10</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(0)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D07</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SCLK(1)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>IOB15_D10N</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Y19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IOB07_D02</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>o_spectrum_bit</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Spectrum</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>IOB15_D11N</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IOB08_D11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>i_config_bit</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Y20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IOB07_D05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>o_spectrum_wr_en</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Spectrum</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>IOB15_D07N</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IOB08_D09</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>o_spectrum_sd_bit</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Spectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IOB08_D08</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>o_spectrum_sd_clk</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Spectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IOB08_D06</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>i_config_wr_en</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Y21</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IOB07_D17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>o_spectrum_clk</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Spectrum</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>IOB15_D06N</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IOB08_D00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>o_spectrum_sd_wr_en</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Spectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>M22</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IOB08_D01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>o_spectrum_sd_sof</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Spectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IOB08_D03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>i_config_sof</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Y22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IOB07_D19</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>o_spectrum_sof</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Spectrum</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>IOB16_D11P</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>o_spectrum_sd_bit</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Spectrum</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>IOB16_D10P</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>o_spectrum_sd_wr_en</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>Spectrum</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>IOB16_D07P</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>o_spectrum_sd_clk</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Spectrum</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D17</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>o_sck(1)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D13</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(1)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D08</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(1)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>IOB00_RST_SOFT_N</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>i_reset</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>D15</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>IOB16_D11N</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>o_spectrum_sd_sof</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>Spectrum</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D21</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(1)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D11</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>o_sck(2)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D09</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(1)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>IOB17_D12P</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>i_config_bit</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>IOB17_D11N</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>i_config_wr_en</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>IOB17_D05P</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>i_config_sof</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D14</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(2)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D18</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(2)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D01</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(1)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D00</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SCLK(5)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D23</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>o_sck(3)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D03</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(3)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D04</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(5)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D05</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(3)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>IOB14_D02</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(5)</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D12</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SCLK(4)</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D11</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(4)</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D13</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(4)</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D03</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(4)</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D14</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(5)</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D09</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SCLK(6)</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>IOB13_D15</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(6)</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D23</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>o_sck(4)</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D22</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SCLK(2)</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D21</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(2)</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D19</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(4)</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D20</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(2)</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D09</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(4)</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D10</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>o_sck(5)</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D18</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(2)</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D17</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SCLK(3)</t>
-        </is>
-      </c>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D08</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(5)</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D11</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(5)</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>U3</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D15</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_SYNC_n(3)</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D16</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(3)</t>
-        </is>
-      </c>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D07</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>o_sck(6)</t>
-        </is>
-      </c>
-      <c r="D59" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D12</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>o_cs_n(6)</t>
-        </is>
-      </c>
-      <c r="D60" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>V3</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D13</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(3)</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>V4</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D14</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_DIN(6)</t>
-        </is>
-      </c>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="17" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D06</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>i_sdi(6)</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>IOB12_D03</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>o_DAC_on_off(6)</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5193,112 +5165,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>ULTRA300 BGA484 - TUT_EGSE top pin placement</t>
-        </is>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Total top-level signals placed</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Source workbook</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C:\3utransat-k160\TUT_EGSE_EP_ads7049_pipeSimplify_branch_k160\script_NX\constraint\ULTRA300_BGA484_Pin_Configuration.xlsx</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Signal source column</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N / Top VHDL signal</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Spectrum</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>Clock</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total constrained pads</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Reset</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>ADC</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>DAC</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Spectrum</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reset note</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>i_reset not constrained through addPads: IOB00_RST_SOFT_N is rejected as malformed IO location by NX.</t>
+        </is>
       </c>
     </row>
   </sheetData>
